--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 05.01.2026 a 11.01.2026.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 05.01.2026 a 11.01.2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19041848-3113-4DFF-92F3-CF82EB69E476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C684F356-CB7E-4446-85C0-1A41D95E7CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="05.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="125">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -270,6 +270,160 @@
   </si>
   <si>
     <t>Dados bancários inválidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELENILSON DE JESUS OLIVEIRA                  </t>
+  </si>
+  <si>
+    <t>Falta de Vistoria;</t>
+  </si>
+  <si>
+    <t>Falta de vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYRO RICARDO GASPAR                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA PEREIRA LIMA DE OLIVEIRA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE DOS SANTOS COELHO                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS EDUARDO PENTEADO BIGLIERE PEREIRA     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENAN RIBEIRO                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGNO LIMA DE BRITO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THABATA DE LUCENA VERONESI                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON VIEIRA DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAQUEL CRISTINA DA SILVA FRIGI               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARBARA VIEIRA COELHO LARANJA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANUSA SANTOS DE OLIVEIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANESSA ALVES DE MORAES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOANA BENEDITA GRANAI BERTONHA               </t>
+  </si>
+  <si>
+    <t>Desistência;</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 05.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIAGO CARDOSO ALVES                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA IMACULADA DE LUCCA                     </t>
+  </si>
+  <si>
+    <t>MARIA HELENA NOBREGA ZELANTE MARYSSAEL DE CAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO BATISTA CLEMER DA SILVA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE EDUARDO YOSHIDA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBSON OLIVEIRA DOS SANTOS                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">J J COMERCIO DE MOTOS LTDA ME                </t>
+  </si>
+  <si>
+    <t>Bônus;</t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:&lt;br&gt; Cópia da apólice congênere c
+om vigência de 2026 a 2027.&lt;br&gt; Endosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE LUIS NESTI                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDA VANESSA DE JESUS SILVA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO PAULO BARBOSA CAMPOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERALDO JOSE DE OLIVEIRA SILVA FILHO          </t>
+  </si>
+  <si>
+    <t>C
+onforme regra de apólices canceladas por vigência de curto prazo,
+houve quebra de vigência de 310 dias, portanto deve-se reduzir 10
+classes de bônus, assim sendo o correto bônus 0. &lt;br&gt;Com a correç
+ão ficou 10x R$ 270,51. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS GUSTAVO DE CASTRO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO BATISTA CARVALHO NUNES                  </t>
+  </si>
+  <si>
+    <t>Proposta em duplicidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIANA CRISTINA PEREIRA SANTOS              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEDNA MARIA MIRANDA BARBOSA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JHONATAN AGUINALDO SALOME GAZOLA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA BARBARA DE FREITAS PIRAHY             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANO SCABENI MONTEIRO                     </t>
+  </si>
+  <si>
+    <t>15 728 627 CRISTIAN GOMES PORCENO DA SILVA ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELTER RODRIGO BOCHIO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIAGO PAIVA VIEIRA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE CARLOS BRITO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAQUEL DO NASCIMENTO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ALBERTO FIGARO BERTIN                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMERCIAL FERREIRA LINCON LTDA EPP           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE DE FATIMA MARTINS CPF 937 060 066 34    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B N QUEIROZ SERVICOS ME                      </t>
   </si>
 </sst>
 </file>
@@ -565,7 +719,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -753,23 +907,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1993,7 +2144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2044,7 +2195,7 @@
         <v>46009</v>
       </c>
       <c r="C2" s="55">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="D2" s="72" t="s">
         <v>10</v>
@@ -2073,15 +2224,15 @@
         <v>73</v>
       </c>
       <c r="C3" s="55">
-        <v>46174</v>
+        <v>46028</v>
       </c>
       <c r="D3" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="63">
         <v>3450190700</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="64" t="s">
         <v>74</v>
       </c>
       <c r="G3" s="42" t="s">
@@ -2098,404 +2249,1297 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C4" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D4" s="75">
+        <v>136011043</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450196871</v>
+      </c>
+      <c r="F4" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="44">
+        <v>46015</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="44"/>
+      <c r="B5" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C5" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D5" s="75">
+        <v>136018928</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450190183</v>
+      </c>
+      <c r="F5" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="44">
+        <v>46009</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C6" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D6" s="75">
+        <v>136019125</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450197476</v>
+      </c>
+      <c r="F6" s="73" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="44">
+        <v>46017</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C7" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D7" s="75">
+        <v>136020099</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450197509</v>
+      </c>
+      <c r="F7" s="73" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="44">
+        <v>46017</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C8" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D8" s="75">
+        <v>136022841</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450197773</v>
+      </c>
+      <c r="F8" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="44">
+        <v>46017</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C9" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D9" s="75">
+        <v>136027454</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450198301</v>
+      </c>
+      <c r="F9" s="73" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="44">
+        <v>46017</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C10" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D10" s="75">
+        <v>136022819</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450197751</v>
+      </c>
+      <c r="F10" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="44">
+        <v>46017</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C11" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D11" s="75">
+        <v>136029118</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450198500</v>
+      </c>
+      <c r="F11" s="73" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="44">
+        <v>46017</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C12" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D12" s="75">
+        <v>136030585</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450198653</v>
+      </c>
+      <c r="F12" s="73" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="44">
+        <v>46017</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C13" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D13" s="75">
+        <v>136032955</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450198928</v>
+      </c>
+      <c r="F13" s="73" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="44">
+        <v>46017</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C14" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D14" s="75">
+        <v>136012754</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450197036</v>
+      </c>
+      <c r="F14" s="73" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="44">
+        <v>46015</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C15" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D15" s="75">
+        <v>136025312</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450190524</v>
+      </c>
+      <c r="F15" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="44">
+        <v>46009</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C16" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D16" s="75">
+        <v>136015341</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450197311</v>
+      </c>
+      <c r="F16" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="44">
+        <v>46015</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="7">
+        <v>46029</v>
+      </c>
+      <c r="C17" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D17" s="75">
+        <v>136078275</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450202976</v>
+      </c>
+      <c r="F17" s="73" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C18" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D18" s="75">
+        <v>136084942</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450203823</v>
+      </c>
+      <c r="F18" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="7">
+        <v>46020</v>
+      </c>
+      <c r="C19" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D19" s="75">
+        <v>136042833</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450199555</v>
+      </c>
+      <c r="F19" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="B20" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C20" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D20" s="75">
+        <v>136085559</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450203955</v>
+      </c>
+      <c r="F20" s="73" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="B21" s="7">
+        <v>46027</v>
+      </c>
+      <c r="C21" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D21" s="75">
+        <v>136095172</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450204846</v>
+      </c>
+      <c r="F21" s="73" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C22" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D22" s="75">
+        <v>136097099</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450203306</v>
+      </c>
+      <c r="F22" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="44"/>
+      <c r="B23" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C23" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D23" s="75">
+        <v>135996519</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450186322</v>
+      </c>
+      <c r="F23" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I23" s="44">
+        <v>46007</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="44"/>
+      <c r="B24" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C24" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D24" s="75">
+        <v>136000257</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450195826</v>
+      </c>
+      <c r="F24" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="44"/>
+      <c r="B25" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C25" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D25" s="75">
+        <v>136013818</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450197124</v>
+      </c>
+      <c r="F25" s="73" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I25" s="44">
+        <v>46015</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="44"/>
+      <c r="B26" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C26" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D26" s="75">
+        <v>136014044</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450197168</v>
+      </c>
+      <c r="F26" s="73" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" s="44">
+        <v>46015</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="44"/>
+      <c r="B27" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C27" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D27" s="75">
+        <v>136014207</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450197180</v>
+      </c>
+      <c r="F27" s="73" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="44">
+        <v>46015</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="44"/>
+      <c r="B28" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C28" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D28" s="75">
+        <v>136014485</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450197201</v>
+      </c>
+      <c r="F28" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="76" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="44"/>
+      <c r="B29" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C29" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D29" s="75">
+        <v>136014792</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450197223</v>
+      </c>
+      <c r="F29" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I29" s="44">
+        <v>46015</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="B30" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C30" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D30" s="75">
+        <v>136014906</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450197256</v>
+      </c>
+      <c r="F30" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I30" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="B31" s="7">
+        <v>46015</v>
+      </c>
+      <c r="C31" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D31" s="75">
+        <v>136015387</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450197322</v>
+      </c>
+      <c r="F31" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I31" s="44">
+        <v>46015</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
+      <c r="B32" s="7">
+        <v>46034</v>
+      </c>
+      <c r="C32" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D32" s="75">
+        <v>136046963</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450199929</v>
+      </c>
+      <c r="F32" s="73" t="s">
+        <v>96</v>
+      </c>
+      <c r="G32" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="I32" s="44">
+        <v>46027</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="24"/>
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C33" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D33" s="75">
+        <v>136020884</v>
+      </c>
+      <c r="E33" s="17">
+        <v>3450197531</v>
+      </c>
+      <c r="F33" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="G33" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I33" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46008</v>
+      </c>
+      <c r="C34" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D34" s="75">
+        <v>136021170</v>
+      </c>
+      <c r="E34" s="17">
+        <v>3450188896</v>
+      </c>
+      <c r="F34" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="44">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C35" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D35" s="75">
+        <v>136022411</v>
+      </c>
+      <c r="E35" s="17">
+        <v>3450197718</v>
+      </c>
+      <c r="F35" s="73" t="s">
+        <v>114</v>
+      </c>
+      <c r="G35" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C36" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D36" s="75">
+        <v>136023129</v>
+      </c>
+      <c r="E36" s="17">
+        <v>3450197795</v>
+      </c>
+      <c r="F36" s="73" t="s">
+        <v>115</v>
+      </c>
+      <c r="G36" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I36" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C37" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D37" s="75">
+        <v>136023243</v>
+      </c>
+      <c r="E37" s="17">
+        <v>3450197828</v>
+      </c>
+      <c r="F37" s="73" t="s">
+        <v>116</v>
+      </c>
+      <c r="G37" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I37" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C38" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D38" s="75">
+        <v>136026532</v>
+      </c>
+      <c r="E38" s="17">
+        <v>3450198235</v>
+      </c>
+      <c r="F38" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="G38" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I38" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C39" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D39" s="75">
+        <v>136027145</v>
+      </c>
+      <c r="E39" s="17">
+        <v>3450198268</v>
+      </c>
+      <c r="F39" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C40" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D40" s="75">
+        <v>136028107</v>
+      </c>
+      <c r="E40" s="17">
+        <v>3450198400</v>
+      </c>
+      <c r="F40" s="73" t="s">
+        <v>119</v>
+      </c>
+      <c r="G40" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I40" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C41" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D41" s="75">
+        <v>136028712</v>
+      </c>
+      <c r="E41" s="17">
+        <v>3450198466</v>
+      </c>
+      <c r="F41" s="73" t="s">
+        <v>120</v>
+      </c>
+      <c r="G41" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I41" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C42" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D42" s="75">
+        <v>136030298</v>
+      </c>
+      <c r="E42" s="17">
+        <v>3450198609</v>
+      </c>
+      <c r="F42" s="73" t="s">
+        <v>121</v>
+      </c>
+      <c r="G42" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I42" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C43" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D43" s="75">
+        <v>136031870</v>
+      </c>
+      <c r="E43" s="17">
+        <v>3450198774</v>
+      </c>
+      <c r="F43" s="73" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C44" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D44" s="75">
+        <v>136031888</v>
+      </c>
+      <c r="E44" s="17">
+        <v>3450198785</v>
+      </c>
+      <c r="F44" s="73" t="s">
+        <v>123</v>
+      </c>
+      <c r="G44" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C45" s="55">
+        <v>46028</v>
+      </c>
+      <c r="D45" s="75">
+        <v>136032495</v>
+      </c>
+      <c r="E45" s="17">
+        <v>3450198851</v>
+      </c>
+      <c r="F45" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="I45" s="44">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="6"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="44"/>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="6"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="44"/>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="6"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="44"/>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="6"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="44"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="6"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="44"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="6"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="24"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:F32 E2:F3">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A32" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A50" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G51" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5529,49 +6573,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540082</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540082</Url>
-      <Description>QAFFA7D2F2TC-2102087286-540082</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5949,7 +6950,59 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540082</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540082</Url>
+      <Description>QAFFA7D2F2TC-2102087286-540082</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -5999,27 +7052,18 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6986EB-BB58-4D50-AC35-394136E3DEB9}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6986EB-BB58-4D50-AC35-394136E3DEB9}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 05.01.2026 a 11.01.2026.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 05.01.2026 a 11.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C684F356-CB7E-4446-85C0-1A41D95E7CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D243D35-693C-49CE-8006-D3C8898641BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="05.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="137">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -425,12 +425,48 @@
   <si>
     <t xml:space="preserve">B N QUEIROZ SERVICOS ME                      </t>
   </si>
+  <si>
+    <t xml:space="preserve">MARCIO COSTA                                 </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 06.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RERISSON FERREIRA DA SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CLAUDIA MORAES DIAS BAPTISTA           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUDGARDA MARTINS FIGUEREDO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELA ASCOLI                               </t>
+  </si>
+  <si>
+    <t>19/12/2025</t>
+  </si>
+  <si>
+    <t>RAFAEL PERKLES TORRES CPF 11559702761</t>
+  </si>
+  <si>
+    <t>Recusa a pedido</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>28/12/2025</t>
+  </si>
+  <si>
+    <t>NILSON VAGNO ARAUJO SILVA CPF 97675571649</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,6 +503,18 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Display"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -482,7 +530,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -658,17 +706,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -677,17 +714,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -719,7 +745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -776,9 +802,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -838,9 +861,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -874,47 +894,69 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1302,22 +1344,22 @@
       <c r="C2" s="7">
         <v>46027</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="63">
+      <c r="E2" s="59">
         <v>3450203878</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="44"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -1338,13 +1380,13 @@
       <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="69" t="s">
+      <c r="G3" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="44">
+      <c r="I3" s="43">
         <v>46009</v>
       </c>
     </row>
@@ -1367,13 +1409,13 @@
       <c r="F4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="G4" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="43">
         <v>46020</v>
       </c>
     </row>
@@ -1396,13 +1438,13 @@
       <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="43">
         <v>46009</v>
       </c>
     </row>
@@ -1425,13 +1467,13 @@
       <c r="F6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>46020</v>
       </c>
     </row>
@@ -1454,13 +1496,13 @@
       <c r="F7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="46" t="s">
+      <c r="H7" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>46013</v>
       </c>
     </row>
@@ -1483,13 +1525,13 @@
       <c r="F8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="69" t="s">
+      <c r="G8" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="46" t="s">
+      <c r="H8" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>46020</v>
       </c>
     </row>
@@ -1512,13 +1554,13 @@
       <c r="F9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1541,13 +1583,13 @@
       <c r="F10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="69" t="s">
+      <c r="G10" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1570,13 +1612,13 @@
       <c r="F11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="69" t="s">
+      <c r="G11" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1599,13 +1641,13 @@
       <c r="F12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="69" t="s">
+      <c r="G12" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1628,13 +1670,13 @@
       <c r="F13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="69" t="s">
+      <c r="G13" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1657,13 +1699,13 @@
       <c r="F14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="69" t="s">
+      <c r="G14" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1686,13 +1728,13 @@
       <c r="F15" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G15" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>46020</v>
       </c>
     </row>
@@ -1715,13 +1757,13 @@
       <c r="F16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1744,13 +1786,13 @@
       <c r="F17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1773,13 +1815,13 @@
       <c r="F18" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="69" t="s">
+      <c r="G18" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1802,13 +1844,13 @@
       <c r="F19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="69" t="s">
+      <c r="G19" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1831,13 +1873,13 @@
       <c r="F20" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="69" t="s">
+      <c r="G20" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>46020</v>
       </c>
     </row>
@@ -1860,13 +1902,13 @@
       <c r="F21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="69" t="s">
+      <c r="G21" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="45" t="s">
+      <c r="H21" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -1889,13 +1931,13 @@
       <c r="F22" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="69" t="s">
+      <c r="G22" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>46020</v>
       </c>
     </row>
@@ -1918,13 +1960,13 @@
       <c r="F23" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G23" s="69" t="s">
+      <c r="G23" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="45" t="s">
+      <c r="H23" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>46010</v>
       </c>
     </row>
@@ -1947,13 +1989,13 @@
       <c r="F24" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="69" t="s">
+      <c r="G24" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>46020</v>
       </c>
     </row>
@@ -1976,13 +2018,13 @@
       <c r="F25" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="69" t="s">
+      <c r="G25" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="45" t="s">
+      <c r="H25" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="43">
         <v>46012</v>
       </c>
     </row>
@@ -2005,13 +2047,13 @@
       <c r="F26" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G26" s="69" t="s">
+      <c r="G26" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="43">
         <v>46020</v>
       </c>
     </row>
@@ -2034,13 +2076,13 @@
       <c r="F27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="69" t="s">
+      <c r="G27" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -2048,7 +2090,7 @@
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="47">
+      <c r="B28" s="46">
         <v>46021</v>
       </c>
       <c r="C28" s="7">
@@ -2063,13 +2105,13 @@
       <c r="F28" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="69" t="s">
+      <c r="G28" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="45" t="s">
+      <c r="H28" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="43">
         <v>46021</v>
       </c>
     </row>
@@ -2092,37 +2134,37 @@
       <c r="F29" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G29" s="69" t="s">
+      <c r="G29" s="62" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="43">
         <v>46020</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
+      <c r="C30" s="24"/>
       <c r="D30" s="22"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="69"/>
+      <c r="G30" s="62"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="42"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="I31" s="43"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -2159,60 +2201,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="48" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="54">
+      <c r="A2" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="52">
         <v>46009</v>
       </c>
-      <c r="C2" s="55">
+      <c r="C2" s="53">
         <v>46028</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="56">
+      <c r="E2" s="54">
         <v>3450187191</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="56" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2223,25 +2265,25 @@
       <c r="B3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="55">
+      <c r="C3" s="53">
         <v>46028</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="63">
+      <c r="E3" s="59">
         <v>3450190700</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="41" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="43" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2252,25 +2294,25 @@
       <c r="B4" s="7">
         <v>46015</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="53">
         <v>46028</v>
       </c>
-      <c r="D4" s="75">
+      <c r="D4" s="22">
         <v>136011043</v>
       </c>
       <c r="E4" s="17">
         <v>3450196871</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="G4" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="43">
         <v>46015</v>
       </c>
     </row>
@@ -2281,25 +2323,25 @@
       <c r="B5" s="7">
         <v>46009</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="53">
         <v>46028</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="22">
         <v>136018928</v>
       </c>
       <c r="E5" s="17">
         <v>3450190183</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="43">
         <v>46009</v>
       </c>
     </row>
@@ -2310,25 +2352,25 @@
       <c r="B6" s="7">
         <v>46017</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="53">
         <v>46028</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="22">
         <v>136019125</v>
       </c>
       <c r="E6" s="17">
         <v>3450197476</v>
       </c>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -2339,25 +2381,25 @@
       <c r="B7" s="7">
         <v>46017</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="53">
         <v>46028</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="22">
         <v>136020099</v>
       </c>
       <c r="E7" s="17">
         <v>3450197509</v>
       </c>
-      <c r="F7" s="73" t="s">
+      <c r="F7" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -2368,25 +2410,25 @@
       <c r="B8" s="7">
         <v>46017</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="53">
         <v>46028</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="22">
         <v>136022841</v>
       </c>
       <c r="E8" s="17">
         <v>3450197773</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="69" t="s">
+      <c r="G8" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -2397,25 +2439,25 @@
       <c r="B9" s="7">
         <v>46017</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="53">
         <v>46028</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="22">
         <v>136027454</v>
       </c>
       <c r="E9" s="17">
         <v>3450198301</v>
       </c>
-      <c r="F9" s="73" t="s">
+      <c r="F9" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="69" t="s">
+      <c r="G9" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -2426,25 +2468,25 @@
       <c r="B10" s="7">
         <v>46017</v>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="53">
         <v>46028</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="22">
         <v>136022819</v>
       </c>
       <c r="E10" s="17">
         <v>3450197751</v>
       </c>
-      <c r="F10" s="73" t="s">
+      <c r="F10" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="69" t="s">
+      <c r="G10" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -2455,25 +2497,25 @@
       <c r="B11" s="7">
         <v>46017</v>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="53">
         <v>46028</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="22">
         <v>136029118</v>
       </c>
       <c r="E11" s="17">
         <v>3450198500</v>
       </c>
-      <c r="F11" s="73" t="s">
+      <c r="F11" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="69" t="s">
+      <c r="G11" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -2484,25 +2526,25 @@
       <c r="B12" s="7">
         <v>46017</v>
       </c>
-      <c r="C12" s="55">
+      <c r="C12" s="53">
         <v>46028</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="22">
         <v>136030585</v>
       </c>
       <c r="E12" s="17">
         <v>3450198653</v>
       </c>
-      <c r="F12" s="73" t="s">
+      <c r="F12" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="69" t="s">
+      <c r="G12" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -2513,25 +2555,25 @@
       <c r="B13" s="7">
         <v>46017</v>
       </c>
-      <c r="C13" s="55">
+      <c r="C13" s="53">
         <v>46028</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="22">
         <v>136032955</v>
       </c>
       <c r="E13" s="17">
         <v>3450198928</v>
       </c>
-      <c r="F13" s="73" t="s">
+      <c r="F13" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="69" t="s">
+      <c r="G13" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -2542,25 +2584,25 @@
       <c r="B14" s="7">
         <v>46015</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="53">
         <v>46028</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="22">
         <v>136012754</v>
       </c>
       <c r="E14" s="17">
         <v>3450197036</v>
       </c>
-      <c r="F14" s="73" t="s">
+      <c r="F14" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="69" t="s">
+      <c r="G14" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>46015</v>
       </c>
     </row>
@@ -2571,25 +2613,25 @@
       <c r="B15" s="7">
         <v>46009</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="53">
         <v>46028</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="22">
         <v>136025312</v>
       </c>
       <c r="E15" s="17">
         <v>3450190524</v>
       </c>
-      <c r="F15" s="73" t="s">
+      <c r="F15" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G15" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>46009</v>
       </c>
     </row>
@@ -2600,25 +2642,25 @@
       <c r="B16" s="7">
         <v>46015</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="53">
         <v>46028</v>
       </c>
-      <c r="D16" s="75">
+      <c r="D16" s="22">
         <v>136015341</v>
       </c>
       <c r="E16" s="17">
         <v>3450197311</v>
       </c>
-      <c r="F16" s="73" t="s">
+      <c r="F16" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="69" t="s">
+      <c r="G16" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>46015</v>
       </c>
     </row>
@@ -2629,25 +2671,25 @@
       <c r="B17" s="7">
         <v>46029</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="53">
         <v>46028</v>
       </c>
-      <c r="D17" s="75">
+      <c r="D17" s="22">
         <v>136078275</v>
       </c>
       <c r="E17" s="17">
         <v>3450202976</v>
       </c>
-      <c r="F17" s="73" t="s">
+      <c r="F17" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="69" t="s">
+      <c r="G17" s="62" t="s">
         <v>92</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -2658,25 +2700,25 @@
       <c r="B18" s="7">
         <v>46024</v>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="53">
         <v>46028</v>
       </c>
-      <c r="D18" s="75">
+      <c r="D18" s="22">
         <v>136084942</v>
       </c>
       <c r="E18" s="17">
         <v>3450203823</v>
       </c>
-      <c r="F18" s="73" t="s">
+      <c r="F18" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G18" s="69" t="s">
+      <c r="G18" s="62" t="s">
         <v>92</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -2687,25 +2729,25 @@
       <c r="B19" s="7">
         <v>46020</v>
       </c>
-      <c r="C19" s="55">
+      <c r="C19" s="53">
         <v>46028</v>
       </c>
-      <c r="D19" s="75">
+      <c r="D19" s="22">
         <v>136042833</v>
       </c>
       <c r="E19" s="17">
         <v>3450199555</v>
       </c>
-      <c r="F19" s="73" t="s">
+      <c r="F19" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="69" t="s">
+      <c r="G19" s="62" t="s">
         <v>92</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -2716,25 +2758,25 @@
       <c r="B20" s="7">
         <v>46034</v>
       </c>
-      <c r="C20" s="55">
+      <c r="C20" s="53">
         <v>46028</v>
       </c>
-      <c r="D20" s="75">
+      <c r="D20" s="22">
         <v>136085559</v>
       </c>
       <c r="E20" s="17">
         <v>3450203955</v>
       </c>
-      <c r="F20" s="73" t="s">
+      <c r="F20" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="69" t="s">
+      <c r="G20" s="62" t="s">
         <v>92</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -2745,25 +2787,25 @@
       <c r="B21" s="7">
         <v>46027</v>
       </c>
-      <c r="C21" s="55">
+      <c r="C21" s="53">
         <v>46028</v>
       </c>
-      <c r="D21" s="75">
+      <c r="D21" s="22">
         <v>136095172</v>
       </c>
       <c r="E21" s="17">
         <v>3450204846</v>
       </c>
-      <c r="F21" s="73" t="s">
+      <c r="F21" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="69" t="s">
+      <c r="G21" s="62" t="s">
         <v>40</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -2774,25 +2816,25 @@
       <c r="B22" s="7">
         <v>46024</v>
       </c>
-      <c r="C22" s="55">
+      <c r="C22" s="53">
         <v>46028</v>
       </c>
-      <c r="D22" s="75">
+      <c r="D22" s="22">
         <v>136097099</v>
       </c>
       <c r="E22" s="17">
         <v>3450203306</v>
       </c>
-      <c r="F22" s="73" t="s">
+      <c r="F22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G22" s="69" t="s">
+      <c r="G22" s="62" t="s">
         <v>92</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -2803,25 +2845,25 @@
       <c r="B23" s="7">
         <v>46007</v>
       </c>
-      <c r="C23" s="55">
+      <c r="C23" s="53">
         <v>46028</v>
       </c>
-      <c r="D23" s="75">
+      <c r="D23" s="22">
         <v>135996519</v>
       </c>
       <c r="E23" s="17">
         <v>3450186322</v>
       </c>
-      <c r="F23" s="73" t="s">
+      <c r="F23" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G23" s="69" t="s">
+      <c r="G23" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>46007</v>
       </c>
     </row>
@@ -2832,25 +2874,25 @@
       <c r="B24" s="7">
         <v>46024</v>
       </c>
-      <c r="C24" s="55">
+      <c r="C24" s="53">
         <v>46028</v>
       </c>
-      <c r="D24" s="75">
+      <c r="D24" s="22">
         <v>136000257</v>
       </c>
       <c r="E24" s="17">
         <v>3450195826</v>
       </c>
-      <c r="F24" s="73" t="s">
+      <c r="F24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="69" t="s">
+      <c r="G24" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="H24" s="76" t="s">
+      <c r="H24" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -2861,25 +2903,25 @@
       <c r="B25" s="7">
         <v>46015</v>
       </c>
-      <c r="C25" s="55">
+      <c r="C25" s="53">
         <v>46028</v>
       </c>
-      <c r="D25" s="75">
+      <c r="D25" s="22">
         <v>136013818</v>
       </c>
       <c r="E25" s="17">
         <v>3450197124</v>
       </c>
-      <c r="F25" s="73" t="s">
+      <c r="F25" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="69" t="s">
+      <c r="G25" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="43">
         <v>46015</v>
       </c>
     </row>
@@ -2890,25 +2932,25 @@
       <c r="B26" s="7">
         <v>46015</v>
       </c>
-      <c r="C26" s="55">
+      <c r="C26" s="53">
         <v>46028</v>
       </c>
-      <c r="D26" s="75">
+      <c r="D26" s="22">
         <v>136014044</v>
       </c>
       <c r="E26" s="17">
         <v>3450197168</v>
       </c>
-      <c r="F26" s="73" t="s">
+      <c r="F26" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G26" s="69" t="s">
+      <c r="G26" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="43">
         <v>46015</v>
       </c>
     </row>
@@ -2919,25 +2961,25 @@
       <c r="B27" s="7">
         <v>46015</v>
       </c>
-      <c r="C27" s="55">
+      <c r="C27" s="53">
         <v>46028</v>
       </c>
-      <c r="D27" s="75">
+      <c r="D27" s="22">
         <v>136014207</v>
       </c>
       <c r="E27" s="17">
         <v>3450197180</v>
       </c>
-      <c r="F27" s="73" t="s">
+      <c r="F27" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G27" s="69" t="s">
+      <c r="G27" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="43">
         <v>46015</v>
       </c>
     </row>
@@ -2948,25 +2990,25 @@
       <c r="B28" s="7">
         <v>46015</v>
       </c>
-      <c r="C28" s="55">
+      <c r="C28" s="53">
         <v>46028</v>
       </c>
-      <c r="D28" s="75">
+      <c r="D28" s="22">
         <v>136014485</v>
       </c>
       <c r="E28" s="17">
         <v>3450197201</v>
       </c>
-      <c r="F28" s="73" t="s">
+      <c r="F28" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G28" s="69" t="s">
+      <c r="G28" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="H28" s="76" t="s">
+      <c r="H28" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -2977,25 +3019,25 @@
       <c r="B29" s="7">
         <v>46015</v>
       </c>
-      <c r="C29" s="55">
+      <c r="C29" s="53">
         <v>46028</v>
       </c>
-      <c r="D29" s="75">
+      <c r="D29" s="22">
         <v>136014792</v>
       </c>
       <c r="E29" s="17">
         <v>3450197223</v>
       </c>
-      <c r="F29" s="73" t="s">
+      <c r="F29" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G29" s="69" t="s">
+      <c r="G29" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="43">
         <v>46015</v>
       </c>
     </row>
@@ -3006,25 +3048,25 @@
       <c r="B30" s="7">
         <v>46045</v>
       </c>
-      <c r="C30" s="55">
+      <c r="C30" s="53">
         <v>46028</v>
       </c>
-      <c r="D30" s="75">
+      <c r="D30" s="22">
         <v>136014906</v>
       </c>
       <c r="E30" s="17">
         <v>3450197256</v>
       </c>
-      <c r="F30" s="73" t="s">
+      <c r="F30" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G30" s="69" t="s">
+      <c r="G30" s="62" t="s">
         <v>70</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -3035,25 +3077,25 @@
       <c r="B31" s="7">
         <v>46015</v>
       </c>
-      <c r="C31" s="55">
+      <c r="C31" s="53">
         <v>46028</v>
       </c>
-      <c r="D31" s="75">
+      <c r="D31" s="22">
         <v>136015387</v>
       </c>
       <c r="E31" s="17">
         <v>3450197322</v>
       </c>
-      <c r="F31" s="73" t="s">
+      <c r="F31" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="69" t="s">
+      <c r="G31" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="43">
         <v>46015</v>
       </c>
     </row>
@@ -3064,25 +3106,25 @@
       <c r="B32" s="7">
         <v>46034</v>
       </c>
-      <c r="C32" s="55">
+      <c r="C32" s="53">
         <v>46028</v>
       </c>
-      <c r="D32" s="75">
+      <c r="D32" s="22">
         <v>136046963</v>
       </c>
       <c r="E32" s="17">
         <v>3450199929</v>
       </c>
-      <c r="F32" s="73" t="s">
+      <c r="F32" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G32" s="69" t="s">
+      <c r="G32" s="62" t="s">
         <v>92</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="43">
         <v>46027</v>
       </c>
     </row>
@@ -3093,25 +3135,25 @@
       <c r="B33" s="7">
         <v>46017</v>
       </c>
-      <c r="C33" s="55">
+      <c r="C33" s="53">
         <v>46028</v>
       </c>
-      <c r="D33" s="75">
+      <c r="D33" s="22">
         <v>136020884</v>
       </c>
       <c r="E33" s="17">
         <v>3450197531</v>
       </c>
-      <c r="F33" s="73" t="s">
+      <c r="F33" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G33" s="69" t="s">
+      <c r="G33" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3122,25 +3164,25 @@
       <c r="B34" s="7">
         <v>46008</v>
       </c>
-      <c r="C34" s="55">
+      <c r="C34" s="53">
         <v>46028</v>
       </c>
-      <c r="D34" s="75">
+      <c r="D34" s="22">
         <v>136021170</v>
       </c>
       <c r="E34" s="17">
         <v>3450188896</v>
       </c>
-      <c r="F34" s="73" t="s">
+      <c r="F34" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G34" s="69" t="s">
+      <c r="G34" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="43">
         <v>46008</v>
       </c>
     </row>
@@ -3151,25 +3193,25 @@
       <c r="B35" s="7">
         <v>46017</v>
       </c>
-      <c r="C35" s="55">
+      <c r="C35" s="53">
         <v>46028</v>
       </c>
-      <c r="D35" s="75">
+      <c r="D35" s="22">
         <v>136022411</v>
       </c>
       <c r="E35" s="17">
         <v>3450197718</v>
       </c>
-      <c r="F35" s="73" t="s">
+      <c r="F35" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G35" s="69" t="s">
+      <c r="G35" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3180,25 +3222,25 @@
       <c r="B36" s="7">
         <v>46017</v>
       </c>
-      <c r="C36" s="55">
+      <c r="C36" s="53">
         <v>46028</v>
       </c>
-      <c r="D36" s="75">
+      <c r="D36" s="22">
         <v>136023129</v>
       </c>
       <c r="E36" s="17">
         <v>3450197795</v>
       </c>
-      <c r="F36" s="73" t="s">
+      <c r="F36" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G36" s="69" t="s">
+      <c r="G36" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3209,25 +3251,25 @@
       <c r="B37" s="7">
         <v>46017</v>
       </c>
-      <c r="C37" s="55">
+      <c r="C37" s="53">
         <v>46028</v>
       </c>
-      <c r="D37" s="75">
+      <c r="D37" s="22">
         <v>136023243</v>
       </c>
       <c r="E37" s="17">
         <v>3450197828</v>
       </c>
-      <c r="F37" s="73" t="s">
+      <c r="F37" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G37" s="69" t="s">
+      <c r="G37" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3238,25 +3280,25 @@
       <c r="B38" s="7">
         <v>46017</v>
       </c>
-      <c r="C38" s="55">
+      <c r="C38" s="53">
         <v>46028</v>
       </c>
-      <c r="D38" s="75">
+      <c r="D38" s="22">
         <v>136026532</v>
       </c>
       <c r="E38" s="17">
         <v>3450198235</v>
       </c>
-      <c r="F38" s="73" t="s">
+      <c r="F38" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G38" s="69" t="s">
+      <c r="G38" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3267,25 +3309,25 @@
       <c r="B39" s="7">
         <v>46017</v>
       </c>
-      <c r="C39" s="55">
+      <c r="C39" s="53">
         <v>46028</v>
       </c>
-      <c r="D39" s="75">
+      <c r="D39" s="22">
         <v>136027145</v>
       </c>
       <c r="E39" s="17">
         <v>3450198268</v>
       </c>
-      <c r="F39" s="73" t="s">
+      <c r="F39" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G39" s="69" t="s">
+      <c r="G39" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3296,25 +3338,25 @@
       <c r="B40" s="7">
         <v>46017</v>
       </c>
-      <c r="C40" s="55">
+      <c r="C40" s="53">
         <v>46028</v>
       </c>
-      <c r="D40" s="75">
+      <c r="D40" s="22">
         <v>136028107</v>
       </c>
       <c r="E40" s="17">
         <v>3450198400</v>
       </c>
-      <c r="F40" s="73" t="s">
+      <c r="F40" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G40" s="69" t="s">
+      <c r="G40" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3325,25 +3367,25 @@
       <c r="B41" s="7">
         <v>46017</v>
       </c>
-      <c r="C41" s="55">
+      <c r="C41" s="53">
         <v>46028</v>
       </c>
-      <c r="D41" s="75">
+      <c r="D41" s="22">
         <v>136028712</v>
       </c>
       <c r="E41" s="17">
         <v>3450198466</v>
       </c>
-      <c r="F41" s="73" t="s">
+      <c r="F41" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G41" s="69" t="s">
+      <c r="G41" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3354,25 +3396,25 @@
       <c r="B42" s="7">
         <v>46017</v>
       </c>
-      <c r="C42" s="55">
+      <c r="C42" s="53">
         <v>46028</v>
       </c>
-      <c r="D42" s="75">
+      <c r="D42" s="22">
         <v>136030298</v>
       </c>
       <c r="E42" s="17">
         <v>3450198609</v>
       </c>
-      <c r="F42" s="73" t="s">
+      <c r="F42" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G42" s="69" t="s">
+      <c r="G42" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I42" s="44">
+      <c r="I42" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3383,25 +3425,25 @@
       <c r="B43" s="7">
         <v>46017</v>
       </c>
-      <c r="C43" s="55">
+      <c r="C43" s="53">
         <v>46028</v>
       </c>
-      <c r="D43" s="75">
+      <c r="D43" s="22">
         <v>136031870</v>
       </c>
       <c r="E43" s="17">
         <v>3450198774</v>
       </c>
-      <c r="F43" s="73" t="s">
+      <c r="F43" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G43" s="69" t="s">
+      <c r="G43" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3412,25 +3454,25 @@
       <c r="B44" s="7">
         <v>46017</v>
       </c>
-      <c r="C44" s="55">
+      <c r="C44" s="53">
         <v>46028</v>
       </c>
-      <c r="D44" s="75">
+      <c r="D44" s="22">
         <v>136031888</v>
       </c>
       <c r="E44" s="17">
         <v>3450198785</v>
       </c>
-      <c r="F44" s="73" t="s">
+      <c r="F44" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G44" s="69" t="s">
+      <c r="G44" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I44" s="44">
+      <c r="I44" s="43">
         <v>46017</v>
       </c>
     </row>
@@ -3441,82 +3483,82 @@
       <c r="B45" s="7">
         <v>46017</v>
       </c>
-      <c r="C45" s="55">
+      <c r="C45" s="53">
         <v>46028</v>
       </c>
-      <c r="D45" s="75">
+      <c r="D45" s="22">
         <v>136032495</v>
       </c>
       <c r="E45" s="17">
         <v>3450198851</v>
       </c>
-      <c r="F45" s="73" t="s">
+      <c r="F45" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="69" t="s">
+      <c r="G45" s="62" t="s">
         <v>77</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="43">
         <v>46017</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="6"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="55"/>
-      <c r="D46" s="74"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="42"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="41"/>
       <c r="H46" s="12"/>
-      <c r="I46" s="44"/>
+      <c r="I46" s="43"/>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="6"/>
       <c r="B47" s="7"/>
-      <c r="C47" s="55"/>
+      <c r="C47" s="53"/>
       <c r="D47" s="22"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11"/>
-      <c r="G47" s="42"/>
+      <c r="G47" s="41"/>
       <c r="H47" s="12"/>
-      <c r="I47" s="44"/>
+      <c r="I47" s="43"/>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="6"/>
       <c r="B48" s="7"/>
-      <c r="C48" s="55"/>
+      <c r="C48" s="53"/>
       <c r="D48" s="22"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11"/>
-      <c r="G48" s="42"/>
+      <c r="G48" s="41"/>
       <c r="H48" s="12"/>
-      <c r="I48" s="44"/>
+      <c r="I48" s="43"/>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="6"/>
       <c r="B49" s="7"/>
-      <c r="C49" s="55"/>
+      <c r="C49" s="53"/>
       <c r="D49" s="22"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11"/>
-      <c r="G49" s="42"/>
+      <c r="G49" s="41"/>
       <c r="H49" s="12"/>
-      <c r="I49" s="44"/>
+      <c r="I49" s="43"/>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="6"/>
       <c r="B50" s="7"/>
-      <c r="C50" s="55"/>
+      <c r="C50" s="53"/>
       <c r="D50" s="22"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11"/>
-      <c r="G50" s="42"/>
+      <c r="G50" s="41"/>
       <c r="H50" s="12"/>
-      <c r="I50" s="44"/>
+      <c r="I50" s="43"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="6"/>
@@ -3525,9 +3567,9 @@
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
       <c r="F51" s="14"/>
-      <c r="G51" s="49"/>
+      <c r="G51" s="47"/>
       <c r="H51" s="14"/>
-      <c r="I51" s="24"/>
+      <c r="I51" s="23"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -3549,7 +3591,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
@@ -3559,7 +3601,7 @@
     <col min="6" max="6" width="30.140625" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="24" customWidth="1"/>
+    <col min="9" max="9" width="21" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3587,7 +3629,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="27" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3595,454 +3637,340 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="44"/>
+      <c r="B2" s="80">
+        <v>46020</v>
+      </c>
+      <c r="C2" s="43">
+        <v>46029</v>
+      </c>
+      <c r="D2" s="75">
+        <v>136060851</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450199478</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="I2" s="43">
+        <v>46028</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="80">
+        <v>46027</v>
+      </c>
+      <c r="C3" s="43">
+        <v>46029</v>
+      </c>
+      <c r="D3" s="75">
+        <v>136104023</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450205814</v>
+      </c>
+      <c r="F3" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="43">
+        <v>46027</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="80">
+        <v>46027</v>
+      </c>
+      <c r="C4" s="43">
+        <v>46029</v>
+      </c>
+      <c r="D4" s="75">
+        <v>136102206</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450205605</v>
+      </c>
+      <c r="F4" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I4" s="43">
+        <v>46028</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="48"/>
+      <c r="B5" s="80">
+        <v>46027</v>
+      </c>
+      <c r="C5" s="43">
+        <v>46029</v>
+      </c>
+      <c r="D5" s="75">
+        <v>136103065</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450205737</v>
+      </c>
+      <c r="F5" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="43">
+        <v>46028</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="80">
+        <v>46027</v>
+      </c>
+      <c r="C6" s="43">
+        <v>46029</v>
+      </c>
+      <c r="D6" s="75">
+        <v>136118256</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450204901</v>
+      </c>
+      <c r="F6" s="71" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="43">
+        <v>46027</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="80">
+        <v>46028</v>
+      </c>
+      <c r="C7" s="43">
+        <v>46029</v>
+      </c>
+      <c r="D7" s="75">
+        <v>136125785</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450207740</v>
+      </c>
+      <c r="F7" s="71" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="43">
+        <v>46028</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="44"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="56"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="25"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="24"/>
       <c r="D9" s="22"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="44"/>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="59"/>
-      <c r="C10" s="25"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="61"/>
+      <c r="G10" s="58"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="25"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="I11" s="43"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="25"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="24"/>
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="61"/>
+      <c r="G12" s="58"/>
       <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="25"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="22"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="59"/>
-      <c r="C14" s="25"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="24"/>
       <c r="D14" s="22"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
+      <c r="G14" s="41"/>
       <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="I14" s="43"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="25"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="24"/>
       <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="61"/>
+      <c r="G15" s="58"/>
       <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="25"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="24"/>
       <c r="D16" s="22"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
+      <c r="G16" s="41"/>
       <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="I16" s="43"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="25"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="24"/>
       <c r="D17" s="22"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A18" s="6"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
+      <c r="C18" s="24"/>
       <c r="D18" s="22"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
+      <c r="C19" s="24"/>
       <c r="D19" s="22"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
+      <c r="G19" s="41"/>
       <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="I19" s="43"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
+      <c r="C20" s="24"/>
       <c r="D20" s="22"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
+      <c r="G20" s="41"/>
       <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="I20" s="43"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
+      <c r="C21" s="24"/>
       <c r="D21" s="22"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="61"/>
+      <c r="G21" s="58"/>
       <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="I21" s="43"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
+      <c r="C22" s="24"/>
       <c r="D22" s="22"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
+      <c r="G22" s="41"/>
       <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="14"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
+      <c r="I22" s="43"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -4050,11 +3978,8 @@
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G22" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
@@ -4075,8 +4000,8 @@
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="44.5703125" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -4111,198 +4036,206 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="15.75">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="B2" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="68">
+        <v>46235</v>
+      </c>
+      <c r="D2" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="67">
+        <v>3450192515</v>
+      </c>
+      <c r="F2" s="79" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="I2" s="76" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="24"/>
+      <c r="B3" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="68">
+        <v>46235</v>
+      </c>
+      <c r="D3" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="73">
+        <v>3450193747</v>
+      </c>
+      <c r="F3" s="74" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="76" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="43"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A5" s="6"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A6" s="6"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="43"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A7" s="6"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A8" s="6"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A9" s="6"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="24"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="26"/>
+      <c r="D11" s="25"/>
       <c r="E11" s="8"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="24"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="78"/>
+      <c r="I11" s="43"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="26"/>
+      <c r="D12" s="25"/>
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="24"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="26"/>
+      <c r="D13" s="25"/>
       <c r="E13" s="8"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="24"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="26"/>
+      <c r="D14" s="25"/>
       <c r="E14" s="8"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="24"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="43"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="A15" s="6"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="26"/>
+      <c r="D15" s="25"/>
       <c r="E15" s="8"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="24"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="26"/>
+      <c r="D16" s="25"/>
       <c r="E16" s="8"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="27"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="24"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -4313,7 +4246,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="24"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -4324,7 +4257,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="24"/>
+      <c r="I18" s="23"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -4335,7 +4268,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -4346,7 +4279,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="23"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -4700,7 +4633,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4765,63 +4698,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="22"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="22"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="33"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="22"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
       <c r="G4" s="19"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="22"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
       <c r="G5" s="19"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -5348,7 +5281,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -5360,232 +5293,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
+      <c r="C2" s="24"/>
       <c r="D2" s="22"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="24"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
+      <c r="C3" s="24"/>
       <c r="D3" s="22"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="22"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="24"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="22"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="24"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
+      <c r="C6" s="24"/>
       <c r="D6" s="22"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="24"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
+      <c r="C7" s="24"/>
       <c r="D7" s="22"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="24"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="22"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="24"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
+      <c r="C9" s="24"/>
       <c r="D9" s="22"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="24"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="24"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="24"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
+      <c r="C12" s="24"/>
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="24"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="23"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="22"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="24"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
+      <c r="C14" s="24"/>
       <c r="D14" s="22"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="24"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
+      <c r="C15" s="24"/>
       <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="24"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
+      <c r="C16" s="24"/>
       <c r="D16" s="22"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="24"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
+      <c r="C17" s="24"/>
       <c r="D17" s="22"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="24"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
+      <c r="C18" s="24"/>
       <c r="D18" s="22"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="24"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="23"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="28"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5594,9 +5527,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="29"/>
+      <c r="G20" s="28"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="23"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5605,9 +5538,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="29"/>
+      <c r="G21" s="28"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="24"/>
+      <c r="I21" s="23"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -5616,9 +5549,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="29"/>
+      <c r="G22" s="28"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="24"/>
+      <c r="I22" s="23"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -5627,9 +5560,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="29"/>
+      <c r="G23" s="28"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="24"/>
+      <c r="I23" s="23"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -5638,9 +5571,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="29"/>
+      <c r="G24" s="28"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="24"/>
+      <c r="I24" s="23"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -5651,7 +5584,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="24"/>
+      <c r="I25" s="23"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -5662,7 +5595,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="24"/>
+      <c r="I26" s="23"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -5673,7 +5606,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="24"/>
+      <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -5684,7 +5617,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="24"/>
+      <c r="I28" s="23"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -5695,7 +5628,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="24"/>
+      <c r="I29" s="23"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -5706,7 +5639,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="24"/>
+      <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -5717,7 +5650,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="24"/>
+      <c r="I31" s="23"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -5728,7 +5661,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="24"/>
+      <c r="I32" s="23"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -5739,7 +5672,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="24"/>
+      <c r="I33" s="23"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -5750,7 +5683,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="24"/>
+      <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -5761,7 +5694,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="24"/>
+      <c r="I35" s="23"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -6051,494 +5984,494 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="43"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="44"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="43"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="42"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="44"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="43"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="42"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="44"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="43"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="42"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="44"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="43"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="44"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="42"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="44"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="43"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="44"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="44"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="43"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="44"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="43"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="42"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="44"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="43"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="43"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="42"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="44"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="43"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="42"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="44"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="43"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="42"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="43"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="43"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="44"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="43"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="44"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="43"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="43"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="43"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="44"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="43"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="44"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="43"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="43"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="44"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="43"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="43"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="42"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="44"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="43"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="43"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="44"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="43"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="43"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="44"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="43"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="43"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="42"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="44"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="43"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="43"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="42"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="44"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="43"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="43"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="42"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="44"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="43"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="43"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="42"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="44"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="43"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="43"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="42"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="44"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="43"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="43"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="42"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="44"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="43"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="42"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
+      <c r="G30" s="41"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="44"/>
+      <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="43"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="42"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
+      <c r="G31" s="41"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="44"/>
+      <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="43"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="42"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="42"/>
+      <c r="G32" s="41"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="44"/>
+      <c r="I32" s="43"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="43"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="42"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="42"/>
+      <c r="G33" s="41"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="44"/>
+      <c r="I33" s="43"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="43"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="42"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="42"/>
+      <c r="G34" s="41"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="44"/>
+      <c r="I34" s="43"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="43"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="42"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="42"/>
+      <c r="G35" s="41"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="44"/>
+      <c r="I35" s="43"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="43"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="42"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
+      <c r="G36" s="41"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="44"/>
+      <c r="I36" s="43"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="43"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="42"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
+      <c r="G37" s="41"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="44"/>
+      <c r="I37" s="43"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="43"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="42"/>
+      <c r="G38" s="41"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="44"/>
+      <c r="I38" s="43"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="43"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="42"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="42"/>
+      <c r="G39" s="41"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="44"/>
+      <c r="I39" s="43"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="43"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="42"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="42"/>
+      <c r="G40" s="41"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="44"/>
+      <c r="I40" s="43"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="43"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="42"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="42"/>
+      <c r="G41" s="41"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="44"/>
+      <c r="I41" s="43"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="43"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="42"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="42"/>
+      <c r="G42" s="41"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="44"/>
+      <c r="I42" s="43"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="30"/>
+      <c r="D43" s="29"/>
       <c r="E43" s="17"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="42"/>
+      <c r="G43" s="41"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
@@ -6573,6 +6506,108 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540082</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540082</Url>
+      <Description>QAFFA7D2F2TC-2102087286-540082</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6950,120 +6985,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540082</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540082</Url>
-      <Description>QAFFA7D2F2TC-2102087286-540082</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6986EB-BB58-4D50-AC35-394136E3DEB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6986EB-BB58-4D50-AC35-394136E3DEB9}"/>
 </file>
--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 05.01.2026 a 11.01.2026.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 05.01.2026 a 11.01.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D243D35-693C-49CE-8006-D3C8898641BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D26FB36B-4AE7-4228-AECF-7185FFB9C909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="05.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="163">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -461,12 +461,109 @@
   <si>
     <t>NILSON VAGNO ARAUJO SILVA CPF 97675571649</t>
   </si>
+  <si>
+    <t>DEBORA GOMES DE MORAES BUENO CPF- 38982255850</t>
+  </si>
+  <si>
+    <t>Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO PAULO MONTEBELO REGIS                   </t>
+  </si>
+  <si>
+    <t>Pedido do segurado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLRS DISTRIBUIDORA DE PNEUS LTDA ME          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falta de vistoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VANDERLEA ALVES DA SILVA                     </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: CRLV, Número do Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO BURILLI SANTOS                         </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Documento do veículo, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STHEFANYE MAFRA BERLINCHES                   </t>
+  </si>
+  <si>
+    <t>RECUSA : FOTOS INCORRETAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS MATOS VIANA                            </t>
+  </si>
+  <si>
+    <t>FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: Chassi. CARENAGEM LATERAL ESQUERDA ARRANHADA - 1PONTO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR SATORI PETRONGARI                      </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 07.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA LEIDJANE LIMA DE ASSUNCAO              </t>
+  </si>
+  <si>
+    <t>PROPOSTA EM DUPLICIDADE&lt;br&gt;&lt;br&gt;Informamos que a p
+roposta em questão se encontra em duplicidade com a apólice 517720
+2562311342593, para prosseguirmos com a emissão se faz necessário
+realizar o cancelamento dela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS FERNANDO OURA HONORIO MARQUES           </t>
+  </si>
+  <si>
+    <t>A apólice que foi utilizada para esta renovação e que nos enviaram
+novamente, consta na Central de Bônus que foi renovada na congêne
+re, por tanto pedimos que nos enviassem a apólice renovada e o end
+osso de cancelamento. O prazo de emissão já acabou e a proposta ca
+ncelou, mas como ainda estamos no prazo da tratativa pedimos que n
+os enviem até amanhã 09/01 os documentos solicitados anteriormente
+, para que possamos analisar e dar reentrada na proposta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAFAELA CAROLINE GONCALVES DE CAMARGOS       </t>
+  </si>
+  <si>
+    <t>É necessária apresentação de um laudo válido que consiste em avali
+ar a situação estrutural do veículo (carroceria, colunas, longarin
+as, torre do amortecedor, painel corta fogo, etc) e também a parte
+da avaliação administrativa e documental do Laudo Cautelar, que c
+onsiste emavaliar (licenciamento, restrições (tributária/judicia
+l/financeira/renajud ) , dívidas, multas , roubo e furto, recall,
+passagens em leilões etc) .&lt;br&gt;Vale ressaltar que a Allianz não ar
+ca com as custas deste Laudo&lt;br&gt;IMPORTANTE: Antes da realização da
+vistoria, confirmar se o laudo atende os requisitos acima e a val
+idade, que deve ser de até 30 dias.&lt;br&gt;Os laudos realizados passar
+ão por uma análiseda Cia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J A AGRO LTDA ME                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEFERSON IVAN PERSCH                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAIANE MARA ORTOLAN PARRA                    </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Frente e lateral do motorista</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -506,12 +603,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Display"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Display"/>
       <scheme val="major"/>
     </font>
@@ -745,7 +836,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -808,9 +899,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -901,9 +989,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -919,44 +1004,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1344,22 +1415,22 @@
       <c r="C2" s="7">
         <v>46027</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="58">
         <v>3450203878</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="43"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -1380,13 +1451,13 @@
       <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="62" t="s">
+      <c r="G3" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="42">
         <v>46009</v>
       </c>
     </row>
@@ -1409,13 +1480,13 @@
       <c r="F4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="62" t="s">
+      <c r="G4" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="42">
         <v>46020</v>
       </c>
     </row>
@@ -1438,13 +1509,13 @@
       <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="62" t="s">
+      <c r="G5" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="42">
         <v>46009</v>
       </c>
     </row>
@@ -1467,13 +1538,13 @@
       <c r="F6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="42">
         <v>46020</v>
       </c>
     </row>
@@ -1496,13 +1567,13 @@
       <c r="F7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="42">
         <v>46013</v>
       </c>
     </row>
@@ -1525,13 +1596,13 @@
       <c r="F8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="62" t="s">
+      <c r="G8" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="42">
         <v>46020</v>
       </c>
     </row>
@@ -1554,13 +1625,13 @@
       <c r="F9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1583,13 +1654,13 @@
       <c r="F10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1612,13 +1683,13 @@
       <c r="F11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="62" t="s">
+      <c r="G11" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1641,13 +1712,13 @@
       <c r="F12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1670,13 +1741,13 @@
       <c r="F13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="62" t="s">
+      <c r="G13" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1699,13 +1770,13 @@
       <c r="F14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="62" t="s">
+      <c r="G14" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1728,13 +1799,13 @@
       <c r="F15" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="42">
         <v>46020</v>
       </c>
     </row>
@@ -1757,13 +1828,13 @@
       <c r="F16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1786,13 +1857,13 @@
       <c r="F17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="62" t="s">
+      <c r="G17" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1815,13 +1886,13 @@
       <c r="F18" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="62" t="s">
+      <c r="G18" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1844,13 +1915,13 @@
       <c r="F19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="62" t="s">
+      <c r="G19" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1873,13 +1944,13 @@
       <c r="F20" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="62" t="s">
+      <c r="G20" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="42">
         <v>46020</v>
       </c>
     </row>
@@ -1902,13 +1973,13 @@
       <c r="F21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="62" t="s">
+      <c r="G21" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -1931,13 +2002,13 @@
       <c r="F22" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="42">
         <v>46020</v>
       </c>
     </row>
@@ -1960,13 +2031,13 @@
       <c r="F23" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G23" s="62" t="s">
+      <c r="G23" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="42">
         <v>46010</v>
       </c>
     </row>
@@ -1989,13 +2060,13 @@
       <c r="F24" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G24" s="62" t="s">
+      <c r="G24" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="42">
         <v>46020</v>
       </c>
     </row>
@@ -2018,13 +2089,13 @@
       <c r="F25" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="62" t="s">
+      <c r="G25" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="42">
         <v>46012</v>
       </c>
     </row>
@@ -2047,13 +2118,13 @@
       <c r="F26" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G26" s="62" t="s">
+      <c r="G26" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="42">
         <v>46020</v>
       </c>
     </row>
@@ -2076,13 +2147,13 @@
       <c r="F27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="62" t="s">
+      <c r="G27" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -2090,7 +2161,7 @@
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="46">
+      <c r="B28" s="45">
         <v>46021</v>
       </c>
       <c r="C28" s="7">
@@ -2105,13 +2176,13 @@
       <c r="F28" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="44" t="s">
+      <c r="H28" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="42">
         <v>46021</v>
       </c>
     </row>
@@ -2134,13 +2205,13 @@
       <c r="F29" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G29" s="62" t="s">
+      <c r="G29" s="60" t="s">
         <v>15</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="42">
         <v>46020</v>
       </c>
     </row>
@@ -2151,20 +2222,20 @@
       <c r="D30" s="22"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="62"/>
+      <c r="G30" s="60"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="43"/>
+      <c r="I30" s="42"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="24"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="41"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="40"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="43"/>
+      <c r="I31" s="42"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -2201,60 +2272,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="48" t="s">
+      <c r="F1" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="48" t="s">
+      <c r="G1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="47" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="52">
+      <c r="A2" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="51">
         <v>46009</v>
       </c>
-      <c r="C2" s="53">
+      <c r="C2" s="52">
         <v>46028</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="54">
+      <c r="E2" s="53">
         <v>3450187191</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="55" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2265,25 +2336,25 @@
       <c r="B3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="53">
+      <c r="C3" s="52">
         <v>46028</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="59">
+      <c r="E3" s="58">
         <v>3450190700</v>
       </c>
-      <c r="F3" s="60" t="s">
+      <c r="F3" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="40" t="s">
         <v>12</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="I3" s="42" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2294,7 +2365,7 @@
       <c r="B4" s="7">
         <v>46015</v>
       </c>
-      <c r="C4" s="53">
+      <c r="C4" s="52">
         <v>46028</v>
       </c>
       <c r="D4" s="22">
@@ -2306,13 +2377,13 @@
       <c r="F4" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="62" t="s">
+      <c r="G4" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="42">
         <v>46015</v>
       </c>
     </row>
@@ -2323,7 +2394,7 @@
       <c r="B5" s="7">
         <v>46009</v>
       </c>
-      <c r="C5" s="53">
+      <c r="C5" s="52">
         <v>46028</v>
       </c>
       <c r="D5" s="22">
@@ -2335,13 +2406,13 @@
       <c r="F5" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="62" t="s">
+      <c r="G5" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="42">
         <v>46009</v>
       </c>
     </row>
@@ -2352,7 +2423,7 @@
       <c r="B6" s="7">
         <v>46017</v>
       </c>
-      <c r="C6" s="53">
+      <c r="C6" s="52">
         <v>46028</v>
       </c>
       <c r="D6" s="22">
@@ -2364,13 +2435,13 @@
       <c r="F6" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -2381,7 +2452,7 @@
       <c r="B7" s="7">
         <v>46017</v>
       </c>
-      <c r="C7" s="53">
+      <c r="C7" s="52">
         <v>46028</v>
       </c>
       <c r="D7" s="22">
@@ -2393,13 +2464,13 @@
       <c r="F7" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -2410,7 +2481,7 @@
       <c r="B8" s="7">
         <v>46017</v>
       </c>
-      <c r="C8" s="53">
+      <c r="C8" s="52">
         <v>46028</v>
       </c>
       <c r="D8" s="22">
@@ -2422,13 +2493,13 @@
       <c r="F8" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="62" t="s">
+      <c r="G8" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -2439,7 +2510,7 @@
       <c r="B9" s="7">
         <v>46017</v>
       </c>
-      <c r="C9" s="53">
+      <c r="C9" s="52">
         <v>46028</v>
       </c>
       <c r="D9" s="22">
@@ -2451,13 +2522,13 @@
       <c r="F9" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -2468,7 +2539,7 @@
       <c r="B10" s="7">
         <v>46017</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="52">
         <v>46028</v>
       </c>
       <c r="D10" s="22">
@@ -2480,13 +2551,13 @@
       <c r="F10" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -2497,7 +2568,7 @@
       <c r="B11" s="7">
         <v>46017</v>
       </c>
-      <c r="C11" s="53">
+      <c r="C11" s="52">
         <v>46028</v>
       </c>
       <c r="D11" s="22">
@@ -2509,13 +2580,13 @@
       <c r="F11" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="62" t="s">
+      <c r="G11" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -2526,7 +2597,7 @@
       <c r="B12" s="7">
         <v>46017</v>
       </c>
-      <c r="C12" s="53">
+      <c r="C12" s="52">
         <v>46028</v>
       </c>
       <c r="D12" s="22">
@@ -2538,13 +2609,13 @@
       <c r="F12" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -2555,7 +2626,7 @@
       <c r="B13" s="7">
         <v>46017</v>
       </c>
-      <c r="C13" s="53">
+      <c r="C13" s="52">
         <v>46028</v>
       </c>
       <c r="D13" s="22">
@@ -2567,13 +2638,13 @@
       <c r="F13" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="62" t="s">
+      <c r="G13" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -2584,7 +2655,7 @@
       <c r="B14" s="7">
         <v>46015</v>
       </c>
-      <c r="C14" s="53">
+      <c r="C14" s="52">
         <v>46028</v>
       </c>
       <c r="D14" s="22">
@@ -2596,13 +2667,13 @@
       <c r="F14" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="62" t="s">
+      <c r="G14" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="42">
         <v>46015</v>
       </c>
     </row>
@@ -2613,7 +2684,7 @@
       <c r="B15" s="7">
         <v>46009</v>
       </c>
-      <c r="C15" s="53">
+      <c r="C15" s="52">
         <v>46028</v>
       </c>
       <c r="D15" s="22">
@@ -2625,13 +2696,13 @@
       <c r="F15" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="42">
         <v>46009</v>
       </c>
     </row>
@@ -2642,7 +2713,7 @@
       <c r="B16" s="7">
         <v>46015</v>
       </c>
-      <c r="C16" s="53">
+      <c r="C16" s="52">
         <v>46028</v>
       </c>
       <c r="D16" s="22">
@@ -2654,13 +2725,13 @@
       <c r="F16" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="42">
         <v>46015</v>
       </c>
     </row>
@@ -2671,7 +2742,7 @@
       <c r="B17" s="7">
         <v>46029</v>
       </c>
-      <c r="C17" s="53">
+      <c r="C17" s="52">
         <v>46028</v>
       </c>
       <c r="D17" s="22">
@@ -2683,13 +2754,13 @@
       <c r="F17" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="62" t="s">
+      <c r="G17" s="60" t="s">
         <v>92</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -2700,7 +2771,7 @@
       <c r="B18" s="7">
         <v>46024</v>
       </c>
-      <c r="C18" s="53">
+      <c r="C18" s="52">
         <v>46028</v>
       </c>
       <c r="D18" s="22">
@@ -2712,13 +2783,13 @@
       <c r="F18" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G18" s="62" t="s">
+      <c r="G18" s="60" t="s">
         <v>92</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -2729,7 +2800,7 @@
       <c r="B19" s="7">
         <v>46020</v>
       </c>
-      <c r="C19" s="53">
+      <c r="C19" s="52">
         <v>46028</v>
       </c>
       <c r="D19" s="22">
@@ -2741,13 +2812,13 @@
       <c r="F19" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="62" t="s">
+      <c r="G19" s="60" t="s">
         <v>92</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -2758,7 +2829,7 @@
       <c r="B20" s="7">
         <v>46034</v>
       </c>
-      <c r="C20" s="53">
+      <c r="C20" s="52">
         <v>46028</v>
       </c>
       <c r="D20" s="22">
@@ -2770,13 +2841,13 @@
       <c r="F20" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="62" t="s">
+      <c r="G20" s="60" t="s">
         <v>92</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -2787,7 +2858,7 @@
       <c r="B21" s="7">
         <v>46027</v>
       </c>
-      <c r="C21" s="53">
+      <c r="C21" s="52">
         <v>46028</v>
       </c>
       <c r="D21" s="22">
@@ -2799,13 +2870,13 @@
       <c r="F21" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="62" t="s">
+      <c r="G21" s="60" t="s">
         <v>40</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -2816,7 +2887,7 @@
       <c r="B22" s="7">
         <v>46024</v>
       </c>
-      <c r="C22" s="53">
+      <c r="C22" s="52">
         <v>46028</v>
       </c>
       <c r="D22" s="22">
@@ -2828,13 +2899,13 @@
       <c r="F22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="60" t="s">
         <v>92</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -2845,7 +2916,7 @@
       <c r="B23" s="7">
         <v>46007</v>
       </c>
-      <c r="C23" s="53">
+      <c r="C23" s="52">
         <v>46028</v>
       </c>
       <c r="D23" s="22">
@@ -2857,13 +2928,13 @@
       <c r="F23" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G23" s="62" t="s">
+      <c r="G23" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="42">
         <v>46007</v>
       </c>
     </row>
@@ -2874,7 +2945,7 @@
       <c r="B24" s="7">
         <v>46024</v>
       </c>
-      <c r="C24" s="53">
+      <c r="C24" s="52">
         <v>46028</v>
       </c>
       <c r="D24" s="22">
@@ -2886,13 +2957,13 @@
       <c r="F24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="62" t="s">
+      <c r="G24" s="60" t="s">
         <v>101</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -2903,7 +2974,7 @@
       <c r="B25" s="7">
         <v>46015</v>
       </c>
-      <c r="C25" s="53">
+      <c r="C25" s="52">
         <v>46028</v>
       </c>
       <c r="D25" s="22">
@@ -2915,13 +2986,13 @@
       <c r="F25" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G25" s="62" t="s">
+      <c r="G25" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="42">
         <v>46015</v>
       </c>
     </row>
@@ -2932,7 +3003,7 @@
       <c r="B26" s="7">
         <v>46015</v>
       </c>
-      <c r="C26" s="53">
+      <c r="C26" s="52">
         <v>46028</v>
       </c>
       <c r="D26" s="22">
@@ -2944,13 +3015,13 @@
       <c r="F26" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G26" s="62" t="s">
+      <c r="G26" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="42">
         <v>46015</v>
       </c>
     </row>
@@ -2961,7 +3032,7 @@
       <c r="B27" s="7">
         <v>46015</v>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="52">
         <v>46028</v>
       </c>
       <c r="D27" s="22">
@@ -2973,13 +3044,13 @@
       <c r="F27" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G27" s="62" t="s">
+      <c r="G27" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="42">
         <v>46015</v>
       </c>
     </row>
@@ -2990,7 +3061,7 @@
       <c r="B28" s="7">
         <v>46015</v>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="52">
         <v>46028</v>
       </c>
       <c r="D28" s="22">
@@ -3002,13 +3073,13 @@
       <c r="F28" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="60" t="s">
         <v>101</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -3019,7 +3090,7 @@
       <c r="B29" s="7">
         <v>46015</v>
       </c>
-      <c r="C29" s="53">
+      <c r="C29" s="52">
         <v>46028</v>
       </c>
       <c r="D29" s="22">
@@ -3031,13 +3102,13 @@
       <c r="F29" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G29" s="62" t="s">
+      <c r="G29" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="42">
         <v>46015</v>
       </c>
     </row>
@@ -3048,7 +3119,7 @@
       <c r="B30" s="7">
         <v>46045</v>
       </c>
-      <c r="C30" s="53">
+      <c r="C30" s="52">
         <v>46028</v>
       </c>
       <c r="D30" s="22">
@@ -3060,13 +3131,13 @@
       <c r="F30" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="60" t="s">
         <v>70</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -3077,7 +3148,7 @@
       <c r="B31" s="7">
         <v>46015</v>
       </c>
-      <c r="C31" s="53">
+      <c r="C31" s="52">
         <v>46028</v>
       </c>
       <c r="D31" s="22">
@@ -3089,13 +3160,13 @@
       <c r="F31" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G31" s="62" t="s">
+      <c r="G31" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="42">
         <v>46015</v>
       </c>
     </row>
@@ -3106,7 +3177,7 @@
       <c r="B32" s="7">
         <v>46034</v>
       </c>
-      <c r="C32" s="53">
+      <c r="C32" s="52">
         <v>46028</v>
       </c>
       <c r="D32" s="22">
@@ -3118,13 +3189,13 @@
       <c r="F32" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G32" s="62" t="s">
+      <c r="G32" s="60" t="s">
         <v>92</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -3135,7 +3206,7 @@
       <c r="B33" s="7">
         <v>46017</v>
       </c>
-      <c r="C33" s="53">
+      <c r="C33" s="52">
         <v>46028</v>
       </c>
       <c r="D33" s="22">
@@ -3147,13 +3218,13 @@
       <c r="F33" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G33" s="62" t="s">
+      <c r="G33" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3164,7 +3235,7 @@
       <c r="B34" s="7">
         <v>46008</v>
       </c>
-      <c r="C34" s="53">
+      <c r="C34" s="52">
         <v>46028</v>
       </c>
       <c r="D34" s="22">
@@ -3176,13 +3247,13 @@
       <c r="F34" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G34" s="62" t="s">
+      <c r="G34" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="42">
         <v>46008</v>
       </c>
     </row>
@@ -3193,7 +3264,7 @@
       <c r="B35" s="7">
         <v>46017</v>
       </c>
-      <c r="C35" s="53">
+      <c r="C35" s="52">
         <v>46028</v>
       </c>
       <c r="D35" s="22">
@@ -3205,13 +3276,13 @@
       <c r="F35" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3222,7 +3293,7 @@
       <c r="B36" s="7">
         <v>46017</v>
       </c>
-      <c r="C36" s="53">
+      <c r="C36" s="52">
         <v>46028</v>
       </c>
       <c r="D36" s="22">
@@ -3234,13 +3305,13 @@
       <c r="F36" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G36" s="62" t="s">
+      <c r="G36" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3251,7 +3322,7 @@
       <c r="B37" s="7">
         <v>46017</v>
       </c>
-      <c r="C37" s="53">
+      <c r="C37" s="52">
         <v>46028</v>
       </c>
       <c r="D37" s="22">
@@ -3263,13 +3334,13 @@
       <c r="F37" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G37" s="62" t="s">
+      <c r="G37" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I37" s="43">
+      <c r="I37" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3280,7 +3351,7 @@
       <c r="B38" s="7">
         <v>46017</v>
       </c>
-      <c r="C38" s="53">
+      <c r="C38" s="52">
         <v>46028</v>
       </c>
       <c r="D38" s="22">
@@ -3292,13 +3363,13 @@
       <c r="F38" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G38" s="62" t="s">
+      <c r="G38" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3309,7 +3380,7 @@
       <c r="B39" s="7">
         <v>46017</v>
       </c>
-      <c r="C39" s="53">
+      <c r="C39" s="52">
         <v>46028</v>
       </c>
       <c r="D39" s="22">
@@ -3321,13 +3392,13 @@
       <c r="F39" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G39" s="62" t="s">
+      <c r="G39" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3338,7 +3409,7 @@
       <c r="B40" s="7">
         <v>46017</v>
       </c>
-      <c r="C40" s="53">
+      <c r="C40" s="52">
         <v>46028</v>
       </c>
       <c r="D40" s="22">
@@ -3350,13 +3421,13 @@
       <c r="F40" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G40" s="62" t="s">
+      <c r="G40" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I40" s="43">
+      <c r="I40" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3367,7 +3438,7 @@
       <c r="B41" s="7">
         <v>46017</v>
       </c>
-      <c r="C41" s="53">
+      <c r="C41" s="52">
         <v>46028</v>
       </c>
       <c r="D41" s="22">
@@ -3379,13 +3450,13 @@
       <c r="F41" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G41" s="62" t="s">
+      <c r="G41" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I41" s="43">
+      <c r="I41" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3396,7 +3467,7 @@
       <c r="B42" s="7">
         <v>46017</v>
       </c>
-      <c r="C42" s="53">
+      <c r="C42" s="52">
         <v>46028</v>
       </c>
       <c r="D42" s="22">
@@ -3408,13 +3479,13 @@
       <c r="F42" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G42" s="62" t="s">
+      <c r="G42" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I42" s="43">
+      <c r="I42" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3425,7 +3496,7 @@
       <c r="B43" s="7">
         <v>46017</v>
       </c>
-      <c r="C43" s="53">
+      <c r="C43" s="52">
         <v>46028</v>
       </c>
       <c r="D43" s="22">
@@ -3437,13 +3508,13 @@
       <c r="F43" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G43" s="62" t="s">
+      <c r="G43" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I43" s="43">
+      <c r="I43" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3454,7 +3525,7 @@
       <c r="B44" s="7">
         <v>46017</v>
       </c>
-      <c r="C44" s="53">
+      <c r="C44" s="52">
         <v>46028</v>
       </c>
       <c r="D44" s="22">
@@ -3466,13 +3537,13 @@
       <c r="F44" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I44" s="43">
+      <c r="I44" s="42">
         <v>46017</v>
       </c>
     </row>
@@ -3483,7 +3554,7 @@
       <c r="B45" s="7">
         <v>46017</v>
       </c>
-      <c r="C45" s="53">
+      <c r="C45" s="52">
         <v>46028</v>
       </c>
       <c r="D45" s="22">
@@ -3495,70 +3566,70 @@
       <c r="F45" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="62" t="s">
+      <c r="G45" s="60" t="s">
         <v>77</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I45" s="43">
+      <c r="I45" s="42">
         <v>46017</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="6"/>
       <c r="B46" s="7"/>
-      <c r="C46" s="53"/>
-      <c r="D46" s="66"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="41"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="40"/>
       <c r="H46" s="12"/>
-      <c r="I46" s="43"/>
+      <c r="I46" s="42"/>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="6"/>
       <c r="B47" s="7"/>
-      <c r="C47" s="53"/>
+      <c r="C47" s="52"/>
       <c r="D47" s="22"/>
       <c r="E47" s="17"/>
       <c r="F47" s="11"/>
-      <c r="G47" s="41"/>
+      <c r="G47" s="40"/>
       <c r="H47" s="12"/>
-      <c r="I47" s="43"/>
+      <c r="I47" s="42"/>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="6"/>
       <c r="B48" s="7"/>
-      <c r="C48" s="53"/>
+      <c r="C48" s="52"/>
       <c r="D48" s="22"/>
       <c r="E48" s="17"/>
       <c r="F48" s="11"/>
-      <c r="G48" s="41"/>
+      <c r="G48" s="40"/>
       <c r="H48" s="12"/>
-      <c r="I48" s="43"/>
+      <c r="I48" s="42"/>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="6"/>
       <c r="B49" s="7"/>
-      <c r="C49" s="53"/>
+      <c r="C49" s="52"/>
       <c r="D49" s="22"/>
       <c r="E49" s="17"/>
       <c r="F49" s="11"/>
-      <c r="G49" s="41"/>
+      <c r="G49" s="40"/>
       <c r="H49" s="12"/>
-      <c r="I49" s="43"/>
+      <c r="I49" s="42"/>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="6"/>
       <c r="B50" s="7"/>
-      <c r="C50" s="53"/>
+      <c r="C50" s="52"/>
       <c r="D50" s="22"/>
       <c r="E50" s="17"/>
       <c r="F50" s="11"/>
-      <c r="G50" s="41"/>
+      <c r="G50" s="40"/>
       <c r="H50" s="12"/>
-      <c r="I50" s="43"/>
+      <c r="I50" s="42"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="6"/>
@@ -3567,7 +3638,7 @@
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
       <c r="F51" s="14"/>
-      <c r="G51" s="47"/>
+      <c r="G51" s="46"/>
       <c r="H51" s="14"/>
       <c r="I51" s="23"/>
     </row>
@@ -3629,7 +3700,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3637,28 +3708,28 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="80">
+      <c r="B2" s="69">
         <v>46020</v>
       </c>
-      <c r="C2" s="43">
+      <c r="C2" s="42">
         <v>46029</v>
       </c>
-      <c r="D2" s="75">
+      <c r="D2" s="22">
         <v>136060851</v>
       </c>
       <c r="E2" s="17">
         <v>3450199478</v>
       </c>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="40" t="s">
         <v>92</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I2" s="43">
+      <c r="I2" s="42">
         <v>46028</v>
       </c>
     </row>
@@ -3666,28 +3737,28 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="80">
+      <c r="B3" s="69">
         <v>46027</v>
       </c>
-      <c r="C3" s="43">
+      <c r="C3" s="42">
         <v>46029</v>
       </c>
-      <c r="D3" s="75">
+      <c r="D3" s="22">
         <v>136104023</v>
       </c>
       <c r="E3" s="17">
         <v>3450205814</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="40" t="s">
         <v>40</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -3695,28 +3766,28 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="80">
+      <c r="B4" s="69">
         <v>46027</v>
       </c>
-      <c r="C4" s="43">
+      <c r="C4" s="42">
         <v>46029</v>
       </c>
-      <c r="D4" s="75">
+      <c r="D4" s="22">
         <v>136102206</v>
       </c>
       <c r="E4" s="17">
         <v>3450205605</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="40" t="s">
         <v>92</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="42">
         <v>46028</v>
       </c>
     </row>
@@ -3724,28 +3795,28 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="80">
+      <c r="B5" s="69">
         <v>46027</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="42">
         <v>46029</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="22">
         <v>136103065</v>
       </c>
       <c r="E5" s="17">
         <v>3450205737</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="40" t="s">
         <v>92</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="42">
         <v>46028</v>
       </c>
     </row>
@@ -3753,28 +3824,28 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="80">
+      <c r="B6" s="69">
         <v>46027</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="42">
         <v>46029</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="22">
         <v>136118256</v>
       </c>
       <c r="E6" s="17">
         <v>3450204901</v>
       </c>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="40" t="s">
         <v>40</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="42">
         <v>46027</v>
       </c>
     </row>
@@ -3782,140 +3853,140 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="80">
+      <c r="B7" s="69">
         <v>46028</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="42">
         <v>46029</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="22">
         <v>136125785</v>
       </c>
       <c r="E7" s="17">
         <v>3450207740</v>
       </c>
-      <c r="F7" s="71" t="s">
+      <c r="F7" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="G7" s="41" t="s">
+      <c r="G7" s="40" t="s">
         <v>40</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="42">
         <v>46028</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="56"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="55"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6"/>
-      <c r="B9" s="57"/>
+      <c r="B9" s="56"/>
       <c r="C9" s="24"/>
       <c r="D9" s="22"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="41"/>
+      <c r="G9" s="40"/>
       <c r="H9" s="11"/>
-      <c r="I9" s="43"/>
+      <c r="I9" s="42"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6"/>
-      <c r="B10" s="57"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="24"/>
       <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="58"/>
+      <c r="G10" s="57"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="43"/>
+      <c r="I10" s="42"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6"/>
-      <c r="B11" s="57"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="24"/>
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="41"/>
+      <c r="G11" s="40"/>
       <c r="H11" s="12"/>
-      <c r="I11" s="43"/>
+      <c r="I11" s="42"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6"/>
-      <c r="B12" s="57"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="24"/>
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="58"/>
+      <c r="G12" s="57"/>
       <c r="H12" s="12"/>
-      <c r="I12" s="43"/>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6"/>
-      <c r="B13" s="57"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="24"/>
       <c r="D13" s="22"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="41"/>
+      <c r="G13" s="40"/>
       <c r="H13" s="12"/>
-      <c r="I13" s="43"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6"/>
-      <c r="B14" s="57"/>
+      <c r="B14" s="56"/>
       <c r="C14" s="24"/>
       <c r="D14" s="22"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="41"/>
+      <c r="G14" s="40"/>
       <c r="H14" s="12"/>
-      <c r="I14" s="43"/>
+      <c r="I14" s="42"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6"/>
-      <c r="B15" s="57"/>
+      <c r="B15" s="56"/>
       <c r="C15" s="24"/>
       <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="58"/>
+      <c r="G15" s="57"/>
       <c r="H15" s="12"/>
-      <c r="I15" s="43"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
-      <c r="B16" s="57"/>
+      <c r="B16" s="56"/>
       <c r="C16" s="24"/>
       <c r="D16" s="22"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
+      <c r="G16" s="40"/>
       <c r="H16" s="12"/>
-      <c r="I16" s="43"/>
+      <c r="I16" s="42"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
-      <c r="B17" s="57"/>
+      <c r="B17" s="56"/>
       <c r="C17" s="24"/>
       <c r="D17" s="22"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="41"/>
+      <c r="G17" s="40"/>
       <c r="H17" s="12"/>
-      <c r="I17" s="43"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -3924,9 +3995,9 @@
       <c r="D18" s="22"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
+      <c r="G18" s="40"/>
       <c r="H18" s="12"/>
-      <c r="I18" s="43"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -3935,9 +4006,9 @@
       <c r="D19" s="22"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="41"/>
+      <c r="G19" s="40"/>
       <c r="H19" s="12"/>
-      <c r="I19" s="43"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -3946,9 +4017,9 @@
       <c r="D20" s="22"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="41"/>
+      <c r="G20" s="40"/>
       <c r="H20" s="12"/>
-      <c r="I20" s="43"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -3957,9 +4028,9 @@
       <c r="D21" s="22"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="58"/>
+      <c r="G21" s="57"/>
       <c r="H21" s="12"/>
-      <c r="I21" s="43"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -3968,9 +4039,9 @@
       <c r="D22" s="22"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="41"/>
+      <c r="G22" s="40"/>
       <c r="H22" s="12"/>
-      <c r="I22" s="43"/>
+      <c r="I22" s="42"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -3993,7 +4064,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -4040,28 +4111,28 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="68">
-        <v>46235</v>
-      </c>
-      <c r="D2" s="69" t="s">
+      <c r="C2" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D2" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="67">
+      <c r="E2" s="17">
         <v>3450192515</v>
       </c>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="70" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="70" t="s">
+      <c r="G2" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="I2" s="76" t="s">
+      <c r="I2" s="67" t="s">
         <v>134</v>
       </c>
     </row>
@@ -4069,571 +4140,477 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="68">
-        <v>46235</v>
-      </c>
-      <c r="D3" s="72" t="s">
+      <c r="C3" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D3" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="73">
+      <c r="E3" s="17">
         <v>3450193747</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="F3" s="70" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="70" t="s">
+      <c r="G3" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="H3" s="77" t="s">
+      <c r="H3" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="I3" s="76" t="s">
+      <c r="I3" s="67" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="6"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="43"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="43"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="43"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="43"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="75"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="78"/>
-      <c r="I8" s="43"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="43"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="43"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="43"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="43"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="43"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="43"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="43"/>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="23"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="23"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="23"/>
+    <row r="4" spans="1:9" ht="15.75">
+      <c r="A4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="24">
+        <v>46029</v>
+      </c>
+      <c r="C4" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450209400</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="73" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="42"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75">
+      <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C5" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D5" s="71">
+        <v>136048418</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450200204</v>
+      </c>
+      <c r="F5" s="70" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="68" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="42">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75">
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7">
+        <v>46021</v>
+      </c>
+      <c r="C6" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D6" s="71">
+        <v>136063224</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450201612</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="I6" s="42">
+        <v>46021</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75">
+      <c r="A7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C7" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D7" s="71">
+        <v>136084074</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450203680</v>
+      </c>
+      <c r="F7" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="42">
+        <v>46024</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75">
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C8" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D8" s="71">
+        <v>136088637</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450204362</v>
+      </c>
+      <c r="F8" s="70" t="s">
+        <v>145</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="68" t="s">
+        <v>146</v>
+      </c>
+      <c r="I8" s="42">
+        <v>46024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75">
+      <c r="A9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C9" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D9" s="71">
+        <v>136086765</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450204098</v>
+      </c>
+      <c r="F9" s="70" t="s">
+        <v>147</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="I9" s="42">
+        <v>46024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75">
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C10" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D10" s="71">
+        <v>136081473</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450203273</v>
+      </c>
+      <c r="F10" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="I10" s="42">
+        <v>46024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C11" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D11" s="71">
+        <v>136086449</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450204054</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="I11" s="42">
+        <v>46024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75">
+      <c r="A12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7">
+        <v>46035</v>
+      </c>
+      <c r="C12" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D12" s="71">
+        <v>136103486</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450205770</v>
+      </c>
+      <c r="F12" s="70" t="s">
+        <v>151</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" s="42">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75">
+      <c r="A13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7">
+        <v>46020</v>
+      </c>
+      <c r="C13" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D13" s="71">
+        <v>136048050</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450200150</v>
+      </c>
+      <c r="F13" s="70" t="s">
+        <v>153</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="74" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="42">
+        <v>46020</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7">
+        <v>46020</v>
+      </c>
+      <c r="C14" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D14" s="71">
+        <v>136022545</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450197730</v>
+      </c>
+      <c r="F14" s="70" t="s">
+        <v>155</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="74" t="s">
+        <v>156</v>
+      </c>
+      <c r="I14" s="72">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75">
+      <c r="A15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="7">
+        <v>46017</v>
+      </c>
+      <c r="C15" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D15" s="71">
+        <v>136027335</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450198280</v>
+      </c>
+      <c r="F15" s="70" t="s">
+        <v>157</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="74" t="s">
+        <v>158</v>
+      </c>
+      <c r="I15" s="42">
+        <v>46028</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75">
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46020</v>
+      </c>
+      <c r="C16" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D16" s="71">
+        <v>136058792</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450200370</v>
+      </c>
+      <c r="F16" s="70" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="I16" s="42">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46022</v>
+      </c>
+      <c r="C17" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D17" s="71">
+        <v>136075706</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450202822</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>160</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="I17" s="42">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>46024</v>
+      </c>
+      <c r="C18" s="65">
+        <v>46030</v>
+      </c>
+      <c r="D18" s="71">
+        <v>136082620</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450203449</v>
+      </c>
+      <c r="F18" s="70" t="s">
+        <v>161</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18" s="42">
+        <v>46024</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="12"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="14"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="23"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="23"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="6"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4641,7 +4618,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G19" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4717,7 +4694,7 @@
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="32"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -4750,8 +4727,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="29"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="23"/>
@@ -5281,7 +5258,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -5297,8 +5274,8 @@
       <c r="D2" s="22"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="33"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="32"/>
       <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
@@ -5310,8 +5287,8 @@
       <c r="D3" s="22"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="32"/>
       <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
@@ -5323,8 +5300,8 @@
       <c r="D4" s="22"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="33"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="32"/>
       <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
@@ -5336,8 +5313,8 @@
       <c r="D5" s="22"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="34"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="33"/>
       <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9">
@@ -5349,8 +5326,8 @@
       <c r="D6" s="22"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="35"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9">
@@ -5362,8 +5339,8 @@
       <c r="D7" s="22"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="35"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="23"/>
     </row>
     <row r="8" spans="1:9">
@@ -5375,8 +5352,8 @@
       <c r="D8" s="22"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="35"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9">
@@ -5388,8 +5365,8 @@
       <c r="D9" s="22"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="33"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9">
@@ -5401,8 +5378,8 @@
       <c r="D10" s="22"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="33"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="32"/>
       <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9">
@@ -5414,8 +5391,8 @@
       <c r="D11" s="22"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="33"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="32"/>
       <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9">
@@ -5427,8 +5404,8 @@
       <c r="D12" s="22"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="33"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="32"/>
       <c r="I12" s="23"/>
     </row>
     <row r="13" spans="1:9">
@@ -5440,8 +5417,8 @@
       <c r="D13" s="22"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="33"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:9">
@@ -5453,8 +5430,8 @@
       <c r="D14" s="22"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="33"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="32"/>
       <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9">
@@ -5466,8 +5443,8 @@
       <c r="D15" s="22"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="33"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="32"/>
       <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9">
@@ -5479,12 +5456,12 @@
       <c r="D16" s="22"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="33"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="32"/>
       <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
@@ -5492,8 +5469,8 @@
       <c r="D17" s="22"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="33"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="32"/>
       <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:9">
@@ -5505,8 +5482,8 @@
       <c r="D18" s="22"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="33"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="32"/>
       <c r="I18" s="23"/>
     </row>
     <row r="19" spans="1:9">
@@ -5514,9 +5491,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="9"/>
       <c r="I19" s="23"/>
     </row>
@@ -5527,7 +5504,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="28"/>
+      <c r="G20" s="27"/>
       <c r="H20" s="9"/>
       <c r="I20" s="23"/>
     </row>
@@ -5538,7 +5515,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="28"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="9"/>
       <c r="I21" s="23"/>
     </row>
@@ -5549,7 +5526,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="28"/>
+      <c r="G22" s="27"/>
       <c r="H22" s="9"/>
       <c r="I22" s="23"/>
     </row>
@@ -5560,7 +5537,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="28"/>
+      <c r="G23" s="27"/>
       <c r="H23" s="9"/>
       <c r="I23" s="23"/>
     </row>
@@ -5571,7 +5548,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="28"/>
+      <c r="G24" s="27"/>
       <c r="H24" s="9"/>
       <c r="I24" s="23"/>
     </row>
@@ -5985,12 +5962,12 @@
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="24"/>
-      <c r="D2" s="42"/>
+      <c r="D2" s="41"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="43"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -5998,12 +5975,12 @@
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="24"/>
-      <c r="D3" s="42"/>
+      <c r="D3" s="41"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="43"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -6011,12 +5988,12 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="42"/>
+      <c r="D4" s="41"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="43"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="42"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -6024,12 +6001,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="42"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="43"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="42"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -6037,12 +6014,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="24"/>
-      <c r="D6" s="42"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="43"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="42"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -6050,12 +6027,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="24"/>
-      <c r="D7" s="42"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="43"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="42"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -6063,12 +6040,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="42"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="43"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="42"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -6076,12 +6053,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="24"/>
-      <c r="D9" s="42"/>
+      <c r="D9" s="41"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="42"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -6089,12 +6066,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="24"/>
-      <c r="D10" s="42"/>
+      <c r="D10" s="41"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="43"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="42"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -6102,12 +6079,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="42"/>
+      <c r="D11" s="41"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="43"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="42"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -6115,12 +6092,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="24"/>
-      <c r="D12" s="42"/>
+      <c r="D12" s="41"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="43"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -6128,12 +6105,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="24"/>
-      <c r="D13" s="42"/>
+      <c r="D13" s="41"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="43"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -6141,12 +6118,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="42"/>
+      <c r="D14" s="41"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="43"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="42"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -6154,12 +6131,12 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="42"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="43"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
@@ -6167,25 +6144,25 @@
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="42"/>
+      <c r="D16" s="41"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="43"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="42"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="42"/>
+      <c r="D17" s="41"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="43"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
@@ -6193,285 +6170,285 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="42"/>
+      <c r="D18" s="41"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="43"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="42"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="42"/>
+      <c r="D19" s="41"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="43"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="42"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="24"/>
-      <c r="D20" s="42"/>
+      <c r="D20" s="41"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="43"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="24"/>
-      <c r="D21" s="42"/>
+      <c r="D21" s="41"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="43"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="24"/>
-      <c r="D22" s="42"/>
+      <c r="D22" s="41"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="43"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
       <c r="C23" s="24"/>
-      <c r="D23" s="42"/>
+      <c r="D23" s="41"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="43"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="42"/>
+      <c r="D24" s="41"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="43"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="42"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="24"/>
-      <c r="D25" s="42"/>
+      <c r="D25" s="41"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="43"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="42"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="24"/>
-      <c r="D26" s="42"/>
+      <c r="D26" s="41"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="43"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="42"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="24"/>
-      <c r="D27" s="42"/>
+      <c r="D27" s="41"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="43"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="42"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="24"/>
-      <c r="D28" s="42"/>
+      <c r="D28" s="41"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="43"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="42"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="46"/>
+      <c r="B29" s="45"/>
       <c r="C29" s="24"/>
-      <c r="D29" s="42"/>
+      <c r="D29" s="41"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="43"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="24"/>
-      <c r="D30" s="42"/>
+      <c r="D30" s="41"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="41"/>
+      <c r="G30" s="40"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="43"/>
+      <c r="I30" s="42"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="24"/>
-      <c r="D31" s="42"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="41"/>
+      <c r="G31" s="40"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="43"/>
+      <c r="I31" s="42"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="24"/>
-      <c r="D32" s="42"/>
+      <c r="D32" s="41"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="41"/>
+      <c r="G32" s="40"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="43"/>
+      <c r="I32" s="42"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="24"/>
-      <c r="D33" s="42"/>
+      <c r="D33" s="41"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="41"/>
+      <c r="G33" s="40"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="43"/>
+      <c r="I33" s="42"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="24"/>
-      <c r="D34" s="42"/>
+      <c r="D34" s="41"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="41"/>
+      <c r="G34" s="40"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="43"/>
+      <c r="I34" s="42"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="24"/>
-      <c r="D35" s="42"/>
+      <c r="D35" s="41"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="41"/>
+      <c r="G35" s="40"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="43"/>
+      <c r="I35" s="42"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="24"/>
-      <c r="D36" s="42"/>
+      <c r="D36" s="41"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="41"/>
+      <c r="G36" s="40"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="43"/>
+      <c r="I36" s="42"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="24"/>
-      <c r="D37" s="42"/>
+      <c r="D37" s="41"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="41"/>
+      <c r="G37" s="40"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="43"/>
+      <c r="I37" s="42"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
       <c r="C38" s="24"/>
-      <c r="D38" s="42"/>
+      <c r="D38" s="41"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="41"/>
+      <c r="G38" s="40"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="43"/>
+      <c r="I38" s="42"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="42"/>
+      <c r="D39" s="41"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="41"/>
+      <c r="G39" s="40"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="43"/>
+      <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
       <c r="C40" s="24"/>
-      <c r="D40" s="42"/>
+      <c r="D40" s="41"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="41"/>
+      <c r="G40" s="40"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="43"/>
+      <c r="I40" s="42"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
       <c r="C41" s="24"/>
-      <c r="D41" s="42"/>
+      <c r="D41" s="41"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="41"/>
+      <c r="G41" s="40"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="43"/>
+      <c r="I41" s="42"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
       <c r="C42" s="24"/>
-      <c r="D42" s="42"/>
+      <c r="D42" s="41"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="41"/>
+      <c r="G42" s="40"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="43"/>
+      <c r="I42" s="42"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="29"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="17"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="41"/>
+      <c r="G43" s="40"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>
@@ -6506,108 +6483,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540082</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540082</Url>
-      <Description>QAFFA7D2F2TC-2102087286-540082</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6985,18 +6860,120 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540082</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-540082</Url>
+      <Description>QAFFA7D2F2TC-2102087286-540082</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6986EB-BB58-4D50-AC35-394136E3DEB9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6986EB-BB58-4D50-AC35-394136E3DEB9}"/>
 </file>